--- a/hospital data analysis.csv.xlsx
+++ b/hospital data analysis.csv.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\pwerbi excel project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3483167E-DCFD-40EA-A30E-6A21E9A9ABFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05339EF9-CEB9-421C-AD5A-DEE2DED06AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{7468EEB1-7F71-44C3-80B8-0B0E32917D42}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{7468EEB1-7F71-44C3-80B8-0B0E32917D42}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5357" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5355" uniqueCount="57">
   <si>
     <t>Patient_ID</t>
   </si>
@@ -215,16 +215,10 @@
     <t>Average of Length_of_Stay</t>
   </si>
   <si>
-    <t>PRACTICE</t>
-  </si>
-  <si>
     <t>Count of Patient_ID</t>
   </si>
   <si>
     <t>Rate of Readmission</t>
-  </si>
-  <si>
-    <t>Percentage</t>
   </si>
   <si>
     <t>Healthcare Analytics Dashboard — Nikita Kandpal</t>
@@ -910,7 +904,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -951,20 +945,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="35" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -974,6 +955,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1889,20 +1879,49 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:marker>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2049,7 +2068,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3264,8 +3282,7 @@
           </a:sp3d>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3405,7 +3422,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -4482,7 +4499,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Length of stay'!$B$1</c:f>
+              <c:f>'Length of stay'!$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4517,7 +4534,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Length of stay'!$A$2:$A$17</c:f>
+              <c:f>'Length of stay'!$B$3:$B$18</c:f>
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
@@ -4570,7 +4587,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Length of stay'!$B$2:$B$17</c:f>
+              <c:f>'Length of stay'!$C$3:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -4970,19 +4987,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5038,19 +5043,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5766,6 +5759,15 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
@@ -8111,6 +8113,15 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
@@ -8171,6 +8182,15 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
@@ -8252,7 +8272,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Length of stay'!$B$1</c:f>
+              <c:f>'Length of stay'!$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8287,7 +8307,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Length of stay'!$A$2:$A$17</c:f>
+              <c:f>'Length of stay'!$B$3:$B$18</c:f>
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
@@ -8340,7 +8360,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Length of stay'!$B$2:$B$17</c:f>
+              <c:f>'Length of stay'!$C$3:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -14267,8 +14287,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Gender">
@@ -14291,7 +14311,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -27419,1134 +27439,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E831B5-CDE6-469A-8C36-3828F53C38F1}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Condition">
-  <location ref="B3:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0">
-      <items count="985">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item x="368"/>
-        <item x="369"/>
-        <item x="370"/>
-        <item x="371"/>
-        <item x="372"/>
-        <item x="373"/>
-        <item x="374"/>
-        <item x="375"/>
-        <item x="376"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="379"/>
-        <item x="380"/>
-        <item x="381"/>
-        <item x="382"/>
-        <item x="383"/>
-        <item x="384"/>
-        <item x="385"/>
-        <item x="386"/>
-        <item x="387"/>
-        <item x="388"/>
-        <item x="389"/>
-        <item x="390"/>
-        <item x="391"/>
-        <item x="392"/>
-        <item x="393"/>
-        <item x="394"/>
-        <item x="395"/>
-        <item x="396"/>
-        <item x="397"/>
-        <item x="398"/>
-        <item x="399"/>
-        <item x="400"/>
-        <item x="401"/>
-        <item x="402"/>
-        <item x="403"/>
-        <item x="404"/>
-        <item x="405"/>
-        <item x="406"/>
-        <item x="407"/>
-        <item x="408"/>
-        <item x="409"/>
-        <item x="410"/>
-        <item x="411"/>
-        <item x="412"/>
-        <item x="413"/>
-        <item x="414"/>
-        <item x="415"/>
-        <item x="416"/>
-        <item x="417"/>
-        <item x="418"/>
-        <item x="419"/>
-        <item x="420"/>
-        <item x="421"/>
-        <item x="422"/>
-        <item x="423"/>
-        <item x="424"/>
-        <item x="425"/>
-        <item x="426"/>
-        <item x="427"/>
-        <item x="428"/>
-        <item x="429"/>
-        <item x="430"/>
-        <item x="431"/>
-        <item x="432"/>
-        <item x="433"/>
-        <item x="434"/>
-        <item x="435"/>
-        <item x="436"/>
-        <item x="437"/>
-        <item x="438"/>
-        <item x="439"/>
-        <item x="440"/>
-        <item x="441"/>
-        <item x="442"/>
-        <item x="443"/>
-        <item x="444"/>
-        <item x="445"/>
-        <item x="446"/>
-        <item x="447"/>
-        <item x="448"/>
-        <item x="449"/>
-        <item x="450"/>
-        <item x="451"/>
-        <item x="452"/>
-        <item x="453"/>
-        <item x="454"/>
-        <item x="455"/>
-        <item x="456"/>
-        <item x="457"/>
-        <item x="458"/>
-        <item x="459"/>
-        <item x="460"/>
-        <item x="461"/>
-        <item x="462"/>
-        <item x="463"/>
-        <item x="464"/>
-        <item x="465"/>
-        <item x="466"/>
-        <item x="467"/>
-        <item x="468"/>
-        <item x="469"/>
-        <item x="470"/>
-        <item x="471"/>
-        <item x="472"/>
-        <item x="473"/>
-        <item x="474"/>
-        <item x="475"/>
-        <item x="476"/>
-        <item x="477"/>
-        <item x="478"/>
-        <item x="479"/>
-        <item x="480"/>
-        <item x="481"/>
-        <item x="482"/>
-        <item x="483"/>
-        <item x="484"/>
-        <item x="485"/>
-        <item x="486"/>
-        <item x="487"/>
-        <item x="488"/>
-        <item x="489"/>
-        <item x="490"/>
-        <item x="491"/>
-        <item x="492"/>
-        <item x="493"/>
-        <item x="494"/>
-        <item x="495"/>
-        <item x="496"/>
-        <item x="497"/>
-        <item x="498"/>
-        <item x="499"/>
-        <item x="500"/>
-        <item x="501"/>
-        <item x="502"/>
-        <item x="503"/>
-        <item x="504"/>
-        <item x="505"/>
-        <item x="506"/>
-        <item x="507"/>
-        <item x="508"/>
-        <item x="509"/>
-        <item x="510"/>
-        <item x="511"/>
-        <item x="512"/>
-        <item x="513"/>
-        <item x="514"/>
-        <item x="515"/>
-        <item x="516"/>
-        <item x="517"/>
-        <item x="518"/>
-        <item x="519"/>
-        <item x="520"/>
-        <item x="521"/>
-        <item x="522"/>
-        <item x="523"/>
-        <item x="524"/>
-        <item x="525"/>
-        <item x="526"/>
-        <item x="527"/>
-        <item x="528"/>
-        <item x="529"/>
-        <item x="530"/>
-        <item x="531"/>
-        <item x="532"/>
-        <item x="533"/>
-        <item x="534"/>
-        <item x="535"/>
-        <item x="536"/>
-        <item x="537"/>
-        <item x="538"/>
-        <item x="539"/>
-        <item x="540"/>
-        <item x="541"/>
-        <item x="542"/>
-        <item x="543"/>
-        <item x="544"/>
-        <item x="545"/>
-        <item x="546"/>
-        <item x="547"/>
-        <item x="548"/>
-        <item x="549"/>
-        <item x="550"/>
-        <item x="551"/>
-        <item x="552"/>
-        <item x="553"/>
-        <item x="554"/>
-        <item x="555"/>
-        <item x="556"/>
-        <item x="557"/>
-        <item x="558"/>
-        <item x="559"/>
-        <item x="560"/>
-        <item x="561"/>
-        <item x="562"/>
-        <item x="563"/>
-        <item x="564"/>
-        <item x="565"/>
-        <item x="566"/>
-        <item x="567"/>
-        <item x="568"/>
-        <item x="569"/>
-        <item x="570"/>
-        <item x="571"/>
-        <item x="572"/>
-        <item x="573"/>
-        <item x="574"/>
-        <item x="575"/>
-        <item x="576"/>
-        <item x="577"/>
-        <item x="578"/>
-        <item x="579"/>
-        <item x="580"/>
-        <item x="581"/>
-        <item x="582"/>
-        <item x="583"/>
-        <item x="584"/>
-        <item x="585"/>
-        <item x="586"/>
-        <item x="587"/>
-        <item x="588"/>
-        <item x="589"/>
-        <item x="590"/>
-        <item x="591"/>
-        <item x="592"/>
-        <item x="593"/>
-        <item x="594"/>
-        <item x="595"/>
-        <item x="596"/>
-        <item x="597"/>
-        <item x="598"/>
-        <item x="599"/>
-        <item x="600"/>
-        <item x="601"/>
-        <item x="602"/>
-        <item x="603"/>
-        <item x="604"/>
-        <item x="605"/>
-        <item x="606"/>
-        <item x="607"/>
-        <item x="608"/>
-        <item x="609"/>
-        <item x="610"/>
-        <item x="611"/>
-        <item x="612"/>
-        <item x="613"/>
-        <item x="614"/>
-        <item x="615"/>
-        <item x="616"/>
-        <item x="617"/>
-        <item x="618"/>
-        <item x="619"/>
-        <item x="620"/>
-        <item x="621"/>
-        <item x="622"/>
-        <item x="623"/>
-        <item x="624"/>
-        <item x="625"/>
-        <item x="626"/>
-        <item x="627"/>
-        <item x="628"/>
-        <item x="629"/>
-        <item x="630"/>
-        <item x="631"/>
-        <item x="632"/>
-        <item x="633"/>
-        <item x="634"/>
-        <item x="635"/>
-        <item x="636"/>
-        <item x="637"/>
-        <item x="638"/>
-        <item x="639"/>
-        <item x="640"/>
-        <item x="641"/>
-        <item x="642"/>
-        <item x="643"/>
-        <item x="644"/>
-        <item x="645"/>
-        <item x="646"/>
-        <item x="647"/>
-        <item x="648"/>
-        <item x="649"/>
-        <item x="650"/>
-        <item x="651"/>
-        <item x="652"/>
-        <item x="653"/>
-        <item x="654"/>
-        <item x="655"/>
-        <item x="656"/>
-        <item x="657"/>
-        <item x="658"/>
-        <item x="659"/>
-        <item x="660"/>
-        <item x="661"/>
-        <item x="662"/>
-        <item x="663"/>
-        <item x="664"/>
-        <item x="665"/>
-        <item x="666"/>
-        <item x="667"/>
-        <item x="668"/>
-        <item x="669"/>
-        <item x="670"/>
-        <item x="671"/>
-        <item x="672"/>
-        <item x="673"/>
-        <item x="674"/>
-        <item x="675"/>
-        <item x="676"/>
-        <item x="677"/>
-        <item x="678"/>
-        <item x="679"/>
-        <item x="680"/>
-        <item x="681"/>
-        <item x="682"/>
-        <item x="683"/>
-        <item x="684"/>
-        <item x="685"/>
-        <item x="686"/>
-        <item x="687"/>
-        <item x="688"/>
-        <item x="689"/>
-        <item x="690"/>
-        <item x="691"/>
-        <item x="692"/>
-        <item x="693"/>
-        <item x="694"/>
-        <item x="695"/>
-        <item x="696"/>
-        <item x="697"/>
-        <item x="698"/>
-        <item x="699"/>
-        <item x="700"/>
-        <item x="701"/>
-        <item x="702"/>
-        <item x="703"/>
-        <item x="704"/>
-        <item x="705"/>
-        <item x="706"/>
-        <item x="707"/>
-        <item x="708"/>
-        <item x="709"/>
-        <item x="710"/>
-        <item x="711"/>
-        <item x="712"/>
-        <item x="713"/>
-        <item x="714"/>
-        <item x="715"/>
-        <item x="716"/>
-        <item x="717"/>
-        <item x="718"/>
-        <item x="719"/>
-        <item x="720"/>
-        <item x="721"/>
-        <item x="722"/>
-        <item x="723"/>
-        <item x="724"/>
-        <item x="725"/>
-        <item x="726"/>
-        <item x="727"/>
-        <item x="728"/>
-        <item x="729"/>
-        <item x="730"/>
-        <item x="731"/>
-        <item x="732"/>
-        <item x="733"/>
-        <item x="734"/>
-        <item x="735"/>
-        <item x="736"/>
-        <item x="737"/>
-        <item x="738"/>
-        <item x="739"/>
-        <item x="740"/>
-        <item x="741"/>
-        <item x="742"/>
-        <item x="743"/>
-        <item x="744"/>
-        <item x="745"/>
-        <item x="746"/>
-        <item x="747"/>
-        <item x="748"/>
-        <item x="749"/>
-        <item x="750"/>
-        <item x="751"/>
-        <item x="752"/>
-        <item x="753"/>
-        <item x="754"/>
-        <item x="755"/>
-        <item x="756"/>
-        <item x="757"/>
-        <item x="758"/>
-        <item x="759"/>
-        <item x="760"/>
-        <item x="761"/>
-        <item x="762"/>
-        <item x="763"/>
-        <item x="764"/>
-        <item x="765"/>
-        <item x="766"/>
-        <item x="767"/>
-        <item x="768"/>
-        <item x="769"/>
-        <item x="770"/>
-        <item x="771"/>
-        <item x="772"/>
-        <item x="773"/>
-        <item x="774"/>
-        <item x="775"/>
-        <item x="776"/>
-        <item x="777"/>
-        <item x="778"/>
-        <item x="779"/>
-        <item x="780"/>
-        <item x="781"/>
-        <item x="782"/>
-        <item x="783"/>
-        <item x="784"/>
-        <item x="785"/>
-        <item x="786"/>
-        <item x="787"/>
-        <item x="788"/>
-        <item x="789"/>
-        <item x="790"/>
-        <item x="791"/>
-        <item x="792"/>
-        <item x="793"/>
-        <item x="794"/>
-        <item x="795"/>
-        <item x="796"/>
-        <item x="797"/>
-        <item x="798"/>
-        <item x="799"/>
-        <item x="800"/>
-        <item x="801"/>
-        <item x="802"/>
-        <item x="803"/>
-        <item x="804"/>
-        <item x="805"/>
-        <item x="806"/>
-        <item x="807"/>
-        <item x="808"/>
-        <item x="809"/>
-        <item x="810"/>
-        <item x="811"/>
-        <item x="812"/>
-        <item x="813"/>
-        <item x="814"/>
-        <item x="815"/>
-        <item x="816"/>
-        <item x="817"/>
-        <item x="818"/>
-        <item x="819"/>
-        <item x="820"/>
-        <item x="821"/>
-        <item x="822"/>
-        <item x="823"/>
-        <item x="824"/>
-        <item x="825"/>
-        <item x="826"/>
-        <item x="827"/>
-        <item x="828"/>
-        <item x="829"/>
-        <item x="830"/>
-        <item x="831"/>
-        <item x="832"/>
-        <item x="833"/>
-        <item x="834"/>
-        <item x="835"/>
-        <item x="836"/>
-        <item x="837"/>
-        <item x="838"/>
-        <item x="839"/>
-        <item x="840"/>
-        <item x="841"/>
-        <item x="842"/>
-        <item x="843"/>
-        <item x="844"/>
-        <item x="845"/>
-        <item x="846"/>
-        <item x="847"/>
-        <item x="848"/>
-        <item x="849"/>
-        <item x="850"/>
-        <item x="851"/>
-        <item x="852"/>
-        <item x="853"/>
-        <item x="854"/>
-        <item x="855"/>
-        <item x="856"/>
-        <item x="857"/>
-        <item x="858"/>
-        <item x="859"/>
-        <item x="860"/>
-        <item x="861"/>
-        <item x="862"/>
-        <item x="863"/>
-        <item x="864"/>
-        <item x="865"/>
-        <item x="866"/>
-        <item x="867"/>
-        <item x="868"/>
-        <item x="869"/>
-        <item x="870"/>
-        <item x="871"/>
-        <item x="872"/>
-        <item x="873"/>
-        <item x="874"/>
-        <item x="875"/>
-        <item x="876"/>
-        <item x="877"/>
-        <item x="878"/>
-        <item x="879"/>
-        <item x="880"/>
-        <item x="881"/>
-        <item x="882"/>
-        <item x="883"/>
-        <item x="884"/>
-        <item x="885"/>
-        <item x="886"/>
-        <item x="887"/>
-        <item x="888"/>
-        <item x="889"/>
-        <item x="890"/>
-        <item x="891"/>
-        <item x="892"/>
-        <item x="893"/>
-        <item x="894"/>
-        <item x="895"/>
-        <item x="896"/>
-        <item x="897"/>
-        <item x="898"/>
-        <item x="899"/>
-        <item x="900"/>
-        <item x="901"/>
-        <item x="902"/>
-        <item x="903"/>
-        <item x="904"/>
-        <item x="905"/>
-        <item x="906"/>
-        <item x="907"/>
-        <item x="908"/>
-        <item x="909"/>
-        <item x="910"/>
-        <item x="911"/>
-        <item x="912"/>
-        <item x="913"/>
-        <item x="914"/>
-        <item x="915"/>
-        <item x="916"/>
-        <item x="917"/>
-        <item x="918"/>
-        <item x="919"/>
-        <item x="920"/>
-        <item x="921"/>
-        <item x="922"/>
-        <item x="923"/>
-        <item x="924"/>
-        <item x="925"/>
-        <item x="926"/>
-        <item x="927"/>
-        <item x="928"/>
-        <item x="929"/>
-        <item x="930"/>
-        <item x="931"/>
-        <item x="932"/>
-        <item x="933"/>
-        <item x="934"/>
-        <item x="935"/>
-        <item x="936"/>
-        <item x="937"/>
-        <item x="938"/>
-        <item x="939"/>
-        <item x="940"/>
-        <item x="941"/>
-        <item x="942"/>
-        <item x="943"/>
-        <item x="944"/>
-        <item x="945"/>
-        <item x="946"/>
-        <item x="947"/>
-        <item x="948"/>
-        <item x="949"/>
-        <item x="950"/>
-        <item x="951"/>
-        <item x="952"/>
-        <item x="953"/>
-        <item x="954"/>
-        <item x="955"/>
-        <item x="956"/>
-        <item x="957"/>
-        <item x="958"/>
-        <item x="959"/>
-        <item x="960"/>
-        <item x="961"/>
-        <item x="962"/>
-        <item x="963"/>
-        <item x="964"/>
-        <item x="965"/>
-        <item x="966"/>
-        <item x="967"/>
-        <item x="968"/>
-        <item x="969"/>
-        <item x="970"/>
-        <item x="971"/>
-        <item x="972"/>
-        <item x="973"/>
-        <item x="974"/>
-        <item x="975"/>
-        <item x="976"/>
-        <item x="977"/>
-        <item x="978"/>
-        <item x="979"/>
-        <item x="980"/>
-        <item x="981"/>
-        <item x="982"/>
-        <item x="983"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="16">
-        <item x="9"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="16">
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count " fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="19" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C412624-B230-46F2-ABD1-83CE4C4BA1B2}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24" rowHeaderCaption="Gender">
   <location ref="G3:H6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -29683,6 +28575,1134 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E831B5-CDE6-469A-8C36-3828F53C38F1}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Condition">
+  <location ref="B3:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0">
+      <items count="985">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item x="368"/>
+        <item x="369"/>
+        <item x="370"/>
+        <item x="371"/>
+        <item x="372"/>
+        <item x="373"/>
+        <item x="374"/>
+        <item x="375"/>
+        <item x="376"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="379"/>
+        <item x="380"/>
+        <item x="381"/>
+        <item x="382"/>
+        <item x="383"/>
+        <item x="384"/>
+        <item x="385"/>
+        <item x="386"/>
+        <item x="387"/>
+        <item x="388"/>
+        <item x="389"/>
+        <item x="390"/>
+        <item x="391"/>
+        <item x="392"/>
+        <item x="393"/>
+        <item x="394"/>
+        <item x="395"/>
+        <item x="396"/>
+        <item x="397"/>
+        <item x="398"/>
+        <item x="399"/>
+        <item x="400"/>
+        <item x="401"/>
+        <item x="402"/>
+        <item x="403"/>
+        <item x="404"/>
+        <item x="405"/>
+        <item x="406"/>
+        <item x="407"/>
+        <item x="408"/>
+        <item x="409"/>
+        <item x="410"/>
+        <item x="411"/>
+        <item x="412"/>
+        <item x="413"/>
+        <item x="414"/>
+        <item x="415"/>
+        <item x="416"/>
+        <item x="417"/>
+        <item x="418"/>
+        <item x="419"/>
+        <item x="420"/>
+        <item x="421"/>
+        <item x="422"/>
+        <item x="423"/>
+        <item x="424"/>
+        <item x="425"/>
+        <item x="426"/>
+        <item x="427"/>
+        <item x="428"/>
+        <item x="429"/>
+        <item x="430"/>
+        <item x="431"/>
+        <item x="432"/>
+        <item x="433"/>
+        <item x="434"/>
+        <item x="435"/>
+        <item x="436"/>
+        <item x="437"/>
+        <item x="438"/>
+        <item x="439"/>
+        <item x="440"/>
+        <item x="441"/>
+        <item x="442"/>
+        <item x="443"/>
+        <item x="444"/>
+        <item x="445"/>
+        <item x="446"/>
+        <item x="447"/>
+        <item x="448"/>
+        <item x="449"/>
+        <item x="450"/>
+        <item x="451"/>
+        <item x="452"/>
+        <item x="453"/>
+        <item x="454"/>
+        <item x="455"/>
+        <item x="456"/>
+        <item x="457"/>
+        <item x="458"/>
+        <item x="459"/>
+        <item x="460"/>
+        <item x="461"/>
+        <item x="462"/>
+        <item x="463"/>
+        <item x="464"/>
+        <item x="465"/>
+        <item x="466"/>
+        <item x="467"/>
+        <item x="468"/>
+        <item x="469"/>
+        <item x="470"/>
+        <item x="471"/>
+        <item x="472"/>
+        <item x="473"/>
+        <item x="474"/>
+        <item x="475"/>
+        <item x="476"/>
+        <item x="477"/>
+        <item x="478"/>
+        <item x="479"/>
+        <item x="480"/>
+        <item x="481"/>
+        <item x="482"/>
+        <item x="483"/>
+        <item x="484"/>
+        <item x="485"/>
+        <item x="486"/>
+        <item x="487"/>
+        <item x="488"/>
+        <item x="489"/>
+        <item x="490"/>
+        <item x="491"/>
+        <item x="492"/>
+        <item x="493"/>
+        <item x="494"/>
+        <item x="495"/>
+        <item x="496"/>
+        <item x="497"/>
+        <item x="498"/>
+        <item x="499"/>
+        <item x="500"/>
+        <item x="501"/>
+        <item x="502"/>
+        <item x="503"/>
+        <item x="504"/>
+        <item x="505"/>
+        <item x="506"/>
+        <item x="507"/>
+        <item x="508"/>
+        <item x="509"/>
+        <item x="510"/>
+        <item x="511"/>
+        <item x="512"/>
+        <item x="513"/>
+        <item x="514"/>
+        <item x="515"/>
+        <item x="516"/>
+        <item x="517"/>
+        <item x="518"/>
+        <item x="519"/>
+        <item x="520"/>
+        <item x="521"/>
+        <item x="522"/>
+        <item x="523"/>
+        <item x="524"/>
+        <item x="525"/>
+        <item x="526"/>
+        <item x="527"/>
+        <item x="528"/>
+        <item x="529"/>
+        <item x="530"/>
+        <item x="531"/>
+        <item x="532"/>
+        <item x="533"/>
+        <item x="534"/>
+        <item x="535"/>
+        <item x="536"/>
+        <item x="537"/>
+        <item x="538"/>
+        <item x="539"/>
+        <item x="540"/>
+        <item x="541"/>
+        <item x="542"/>
+        <item x="543"/>
+        <item x="544"/>
+        <item x="545"/>
+        <item x="546"/>
+        <item x="547"/>
+        <item x="548"/>
+        <item x="549"/>
+        <item x="550"/>
+        <item x="551"/>
+        <item x="552"/>
+        <item x="553"/>
+        <item x="554"/>
+        <item x="555"/>
+        <item x="556"/>
+        <item x="557"/>
+        <item x="558"/>
+        <item x="559"/>
+        <item x="560"/>
+        <item x="561"/>
+        <item x="562"/>
+        <item x="563"/>
+        <item x="564"/>
+        <item x="565"/>
+        <item x="566"/>
+        <item x="567"/>
+        <item x="568"/>
+        <item x="569"/>
+        <item x="570"/>
+        <item x="571"/>
+        <item x="572"/>
+        <item x="573"/>
+        <item x="574"/>
+        <item x="575"/>
+        <item x="576"/>
+        <item x="577"/>
+        <item x="578"/>
+        <item x="579"/>
+        <item x="580"/>
+        <item x="581"/>
+        <item x="582"/>
+        <item x="583"/>
+        <item x="584"/>
+        <item x="585"/>
+        <item x="586"/>
+        <item x="587"/>
+        <item x="588"/>
+        <item x="589"/>
+        <item x="590"/>
+        <item x="591"/>
+        <item x="592"/>
+        <item x="593"/>
+        <item x="594"/>
+        <item x="595"/>
+        <item x="596"/>
+        <item x="597"/>
+        <item x="598"/>
+        <item x="599"/>
+        <item x="600"/>
+        <item x="601"/>
+        <item x="602"/>
+        <item x="603"/>
+        <item x="604"/>
+        <item x="605"/>
+        <item x="606"/>
+        <item x="607"/>
+        <item x="608"/>
+        <item x="609"/>
+        <item x="610"/>
+        <item x="611"/>
+        <item x="612"/>
+        <item x="613"/>
+        <item x="614"/>
+        <item x="615"/>
+        <item x="616"/>
+        <item x="617"/>
+        <item x="618"/>
+        <item x="619"/>
+        <item x="620"/>
+        <item x="621"/>
+        <item x="622"/>
+        <item x="623"/>
+        <item x="624"/>
+        <item x="625"/>
+        <item x="626"/>
+        <item x="627"/>
+        <item x="628"/>
+        <item x="629"/>
+        <item x="630"/>
+        <item x="631"/>
+        <item x="632"/>
+        <item x="633"/>
+        <item x="634"/>
+        <item x="635"/>
+        <item x="636"/>
+        <item x="637"/>
+        <item x="638"/>
+        <item x="639"/>
+        <item x="640"/>
+        <item x="641"/>
+        <item x="642"/>
+        <item x="643"/>
+        <item x="644"/>
+        <item x="645"/>
+        <item x="646"/>
+        <item x="647"/>
+        <item x="648"/>
+        <item x="649"/>
+        <item x="650"/>
+        <item x="651"/>
+        <item x="652"/>
+        <item x="653"/>
+        <item x="654"/>
+        <item x="655"/>
+        <item x="656"/>
+        <item x="657"/>
+        <item x="658"/>
+        <item x="659"/>
+        <item x="660"/>
+        <item x="661"/>
+        <item x="662"/>
+        <item x="663"/>
+        <item x="664"/>
+        <item x="665"/>
+        <item x="666"/>
+        <item x="667"/>
+        <item x="668"/>
+        <item x="669"/>
+        <item x="670"/>
+        <item x="671"/>
+        <item x="672"/>
+        <item x="673"/>
+        <item x="674"/>
+        <item x="675"/>
+        <item x="676"/>
+        <item x="677"/>
+        <item x="678"/>
+        <item x="679"/>
+        <item x="680"/>
+        <item x="681"/>
+        <item x="682"/>
+        <item x="683"/>
+        <item x="684"/>
+        <item x="685"/>
+        <item x="686"/>
+        <item x="687"/>
+        <item x="688"/>
+        <item x="689"/>
+        <item x="690"/>
+        <item x="691"/>
+        <item x="692"/>
+        <item x="693"/>
+        <item x="694"/>
+        <item x="695"/>
+        <item x="696"/>
+        <item x="697"/>
+        <item x="698"/>
+        <item x="699"/>
+        <item x="700"/>
+        <item x="701"/>
+        <item x="702"/>
+        <item x="703"/>
+        <item x="704"/>
+        <item x="705"/>
+        <item x="706"/>
+        <item x="707"/>
+        <item x="708"/>
+        <item x="709"/>
+        <item x="710"/>
+        <item x="711"/>
+        <item x="712"/>
+        <item x="713"/>
+        <item x="714"/>
+        <item x="715"/>
+        <item x="716"/>
+        <item x="717"/>
+        <item x="718"/>
+        <item x="719"/>
+        <item x="720"/>
+        <item x="721"/>
+        <item x="722"/>
+        <item x="723"/>
+        <item x="724"/>
+        <item x="725"/>
+        <item x="726"/>
+        <item x="727"/>
+        <item x="728"/>
+        <item x="729"/>
+        <item x="730"/>
+        <item x="731"/>
+        <item x="732"/>
+        <item x="733"/>
+        <item x="734"/>
+        <item x="735"/>
+        <item x="736"/>
+        <item x="737"/>
+        <item x="738"/>
+        <item x="739"/>
+        <item x="740"/>
+        <item x="741"/>
+        <item x="742"/>
+        <item x="743"/>
+        <item x="744"/>
+        <item x="745"/>
+        <item x="746"/>
+        <item x="747"/>
+        <item x="748"/>
+        <item x="749"/>
+        <item x="750"/>
+        <item x="751"/>
+        <item x="752"/>
+        <item x="753"/>
+        <item x="754"/>
+        <item x="755"/>
+        <item x="756"/>
+        <item x="757"/>
+        <item x="758"/>
+        <item x="759"/>
+        <item x="760"/>
+        <item x="761"/>
+        <item x="762"/>
+        <item x="763"/>
+        <item x="764"/>
+        <item x="765"/>
+        <item x="766"/>
+        <item x="767"/>
+        <item x="768"/>
+        <item x="769"/>
+        <item x="770"/>
+        <item x="771"/>
+        <item x="772"/>
+        <item x="773"/>
+        <item x="774"/>
+        <item x="775"/>
+        <item x="776"/>
+        <item x="777"/>
+        <item x="778"/>
+        <item x="779"/>
+        <item x="780"/>
+        <item x="781"/>
+        <item x="782"/>
+        <item x="783"/>
+        <item x="784"/>
+        <item x="785"/>
+        <item x="786"/>
+        <item x="787"/>
+        <item x="788"/>
+        <item x="789"/>
+        <item x="790"/>
+        <item x="791"/>
+        <item x="792"/>
+        <item x="793"/>
+        <item x="794"/>
+        <item x="795"/>
+        <item x="796"/>
+        <item x="797"/>
+        <item x="798"/>
+        <item x="799"/>
+        <item x="800"/>
+        <item x="801"/>
+        <item x="802"/>
+        <item x="803"/>
+        <item x="804"/>
+        <item x="805"/>
+        <item x="806"/>
+        <item x="807"/>
+        <item x="808"/>
+        <item x="809"/>
+        <item x="810"/>
+        <item x="811"/>
+        <item x="812"/>
+        <item x="813"/>
+        <item x="814"/>
+        <item x="815"/>
+        <item x="816"/>
+        <item x="817"/>
+        <item x="818"/>
+        <item x="819"/>
+        <item x="820"/>
+        <item x="821"/>
+        <item x="822"/>
+        <item x="823"/>
+        <item x="824"/>
+        <item x="825"/>
+        <item x="826"/>
+        <item x="827"/>
+        <item x="828"/>
+        <item x="829"/>
+        <item x="830"/>
+        <item x="831"/>
+        <item x="832"/>
+        <item x="833"/>
+        <item x="834"/>
+        <item x="835"/>
+        <item x="836"/>
+        <item x="837"/>
+        <item x="838"/>
+        <item x="839"/>
+        <item x="840"/>
+        <item x="841"/>
+        <item x="842"/>
+        <item x="843"/>
+        <item x="844"/>
+        <item x="845"/>
+        <item x="846"/>
+        <item x="847"/>
+        <item x="848"/>
+        <item x="849"/>
+        <item x="850"/>
+        <item x="851"/>
+        <item x="852"/>
+        <item x="853"/>
+        <item x="854"/>
+        <item x="855"/>
+        <item x="856"/>
+        <item x="857"/>
+        <item x="858"/>
+        <item x="859"/>
+        <item x="860"/>
+        <item x="861"/>
+        <item x="862"/>
+        <item x="863"/>
+        <item x="864"/>
+        <item x="865"/>
+        <item x="866"/>
+        <item x="867"/>
+        <item x="868"/>
+        <item x="869"/>
+        <item x="870"/>
+        <item x="871"/>
+        <item x="872"/>
+        <item x="873"/>
+        <item x="874"/>
+        <item x="875"/>
+        <item x="876"/>
+        <item x="877"/>
+        <item x="878"/>
+        <item x="879"/>
+        <item x="880"/>
+        <item x="881"/>
+        <item x="882"/>
+        <item x="883"/>
+        <item x="884"/>
+        <item x="885"/>
+        <item x="886"/>
+        <item x="887"/>
+        <item x="888"/>
+        <item x="889"/>
+        <item x="890"/>
+        <item x="891"/>
+        <item x="892"/>
+        <item x="893"/>
+        <item x="894"/>
+        <item x="895"/>
+        <item x="896"/>
+        <item x="897"/>
+        <item x="898"/>
+        <item x="899"/>
+        <item x="900"/>
+        <item x="901"/>
+        <item x="902"/>
+        <item x="903"/>
+        <item x="904"/>
+        <item x="905"/>
+        <item x="906"/>
+        <item x="907"/>
+        <item x="908"/>
+        <item x="909"/>
+        <item x="910"/>
+        <item x="911"/>
+        <item x="912"/>
+        <item x="913"/>
+        <item x="914"/>
+        <item x="915"/>
+        <item x="916"/>
+        <item x="917"/>
+        <item x="918"/>
+        <item x="919"/>
+        <item x="920"/>
+        <item x="921"/>
+        <item x="922"/>
+        <item x="923"/>
+        <item x="924"/>
+        <item x="925"/>
+        <item x="926"/>
+        <item x="927"/>
+        <item x="928"/>
+        <item x="929"/>
+        <item x="930"/>
+        <item x="931"/>
+        <item x="932"/>
+        <item x="933"/>
+        <item x="934"/>
+        <item x="935"/>
+        <item x="936"/>
+        <item x="937"/>
+        <item x="938"/>
+        <item x="939"/>
+        <item x="940"/>
+        <item x="941"/>
+        <item x="942"/>
+        <item x="943"/>
+        <item x="944"/>
+        <item x="945"/>
+        <item x="946"/>
+        <item x="947"/>
+        <item x="948"/>
+        <item x="949"/>
+        <item x="950"/>
+        <item x="951"/>
+        <item x="952"/>
+        <item x="953"/>
+        <item x="954"/>
+        <item x="955"/>
+        <item x="956"/>
+        <item x="957"/>
+        <item x="958"/>
+        <item x="959"/>
+        <item x="960"/>
+        <item x="961"/>
+        <item x="962"/>
+        <item x="963"/>
+        <item x="964"/>
+        <item x="965"/>
+        <item x="966"/>
+        <item x="967"/>
+        <item x="968"/>
+        <item x="969"/>
+        <item x="970"/>
+        <item x="971"/>
+        <item x="972"/>
+        <item x="973"/>
+        <item x="974"/>
+        <item x="975"/>
+        <item x="976"/>
+        <item x="977"/>
+        <item x="978"/>
+        <item x="979"/>
+        <item x="980"/>
+        <item x="981"/>
+        <item x="982"/>
+        <item x="983"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="16">
+        <item x="9"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count " fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{509BEEF8-D100-44AD-B651-7A70E1C4260E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="B2:C18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
@@ -29846,7 +29866,7 @@
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FF2E107E-6442-4B36-811B-7C73889B3E91}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="A1:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B2:C18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
       <items count="985">
@@ -31080,42 +31100,42 @@
     <dataField name="Count of Patient_ID" fld="0" subtotal="count" baseField="3" baseItem="13"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="0">
+    <format dxfId="9">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="7">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="6">
       <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="5">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="4">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -33730,7 +33750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5185E9A6-5FDD-4D32-BF4F-381697A4C529}">
-  <dimension ref="A1:L986"/>
+  <dimension ref="A1:J986"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -33745,21 +33765,21 @@
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="24"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -33790,11 +33810,8 @@
       <c r="J2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -33826,7 +33843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -33858,7 +33875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -33890,7 +33907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -33922,7 +33939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -33954,7 +33971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -33985,12 +34002,8 @@
       <c r="J8" s="4">
         <v>4</v>
       </c>
-      <c r="L8">
-        <f>COUNTIF(D:D, "Cancer")</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -34022,7 +34035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -34053,12 +34066,8 @@
       <c r="J10" s="4">
         <v>4</v>
       </c>
-      <c r="L10">
-        <f>AVERAGEIF(D:D, "Cancer", F:F)</f>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -34090,7 +34099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -34121,12 +34130,8 @@
       <c r="J12" s="4">
         <v>5</v>
       </c>
-      <c r="L12">
-        <f>MAX(F:F)</f>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -34158,7 +34163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -34189,12 +34194,8 @@
       <c r="J14" s="4">
         <v>3</v>
       </c>
-      <c r="L14">
-        <f>MIN(F:F)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -34226,7 +34227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -65344,15 +65345,12 @@
       <c r="H3" t="s">
         <v>51</v>
       </c>
-      <c r="I3" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4">
         <v>67</v>
       </c>
       <c r="G4" s="12" t="s">
@@ -65366,7 +65364,7 @@
       <c r="B5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5">
         <v>67</v>
       </c>
       <c r="G5" s="12" t="s">
@@ -65380,7 +65378,7 @@
       <c r="B6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6">
         <v>66</v>
       </c>
       <c r="G6" s="12" t="s">
@@ -65394,7 +65392,7 @@
       <c r="B7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7">
         <v>66</v>
       </c>
     </row>
@@ -65402,7 +65400,7 @@
       <c r="B8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8">
         <v>66</v>
       </c>
     </row>
@@ -65410,7 +65408,7 @@
       <c r="B9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9">
         <v>66</v>
       </c>
     </row>
@@ -65418,7 +65416,7 @@
       <c r="B10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10">
         <v>66</v>
       </c>
     </row>
@@ -65426,7 +65424,7 @@
       <c r="B11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11">
         <v>66</v>
       </c>
     </row>
@@ -65434,7 +65432,7 @@
       <c r="B12" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12">
         <v>65</v>
       </c>
     </row>
@@ -65442,7 +65440,7 @@
       <c r="B13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13">
         <v>65</v>
       </c>
       <c r="J13" s="14"/>
@@ -65451,7 +65449,7 @@
       <c r="B14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14">
         <v>65</v>
       </c>
     </row>
@@ -65459,7 +65457,7 @@
       <c r="B15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15">
         <v>65</v>
       </c>
     </row>
@@ -65467,7 +65465,7 @@
       <c r="B16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16">
         <v>65</v>
       </c>
     </row>
@@ -65475,7 +65473,7 @@
       <c r="B17" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17">
         <v>65</v>
       </c>
     </row>
@@ -65483,7 +65481,7 @@
       <c r="B18" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18">
         <v>64</v>
       </c>
     </row>
@@ -65491,7 +65489,7 @@
       <c r="B19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19">
         <v>984</v>
       </c>
     </row>
@@ -65522,7 +65520,7 @@
       <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="16">
         <v>25000</v>
       </c>
     </row>
@@ -65530,7 +65528,7 @@
       <c r="B4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="16">
         <v>20000</v>
       </c>
     </row>
@@ -65538,7 +65536,7 @@
       <c r="B5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="16">
         <v>18000</v>
       </c>
     </row>
@@ -65546,7 +65544,7 @@
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="16">
         <v>15000</v>
       </c>
     </row>
@@ -65554,7 +65552,7 @@
       <c r="B7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="16">
         <v>12000</v>
       </c>
     </row>
@@ -65562,7 +65560,7 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="16">
         <v>10000</v>
       </c>
     </row>
@@ -65570,7 +65568,7 @@
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="16">
         <v>8000</v>
       </c>
     </row>
@@ -65578,7 +65576,7 @@
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="16">
         <v>6000</v>
       </c>
     </row>
@@ -65586,7 +65584,7 @@
       <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="16">
         <v>4000</v>
       </c>
     </row>
@@ -65594,7 +65592,7 @@
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="16">
         <v>3000</v>
       </c>
     </row>
@@ -65602,7 +65600,7 @@
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="16">
         <v>2000</v>
       </c>
     </row>
@@ -65610,7 +65608,7 @@
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="16">
         <v>1000</v>
       </c>
     </row>
@@ -65618,7 +65616,7 @@
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="16">
         <v>800</v>
       </c>
     </row>
@@ -65626,7 +65624,7 @@
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="16">
         <v>500</v>
       </c>
     </row>
@@ -65634,7 +65632,7 @@
       <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="16">
         <v>100</v>
       </c>
     </row>
@@ -65642,7 +65640,7 @@
       <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="16">
         <v>8367.4796747967484</v>
       </c>
     </row>
@@ -65654,146 +65652,146 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EC54FF7-3080-4FD1-A56E-74273C53B652}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="B2:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B2">
+      <c r="C3">
         <v>34.242424242424242</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B3">
+      <c r="C4">
         <v>37.439393939393938</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B4">
+      <c r="C5">
         <v>42.651515151515149</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B5">
+      <c r="C6">
         <v>35.523076923076921</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B6">
+      <c r="C7">
         <v>36.092307692307692</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B7">
+      <c r="C8">
         <v>34.257575757575758</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B8">
+      <c r="C9">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B9">
+      <c r="C10">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
+      <c r="C11">
         <v>38.215384615384615</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B11">
+      <c r="C12">
         <v>35.515151515151516</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B12">
+      <c r="C13">
         <v>36.46153846153846</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B13">
+      <c r="C14">
         <v>37.859375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B14">
+      <c r="C15">
         <v>41.584615384615383</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B15">
+      <c r="C16">
         <v>34.661538461538463</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B16">
+      <c r="C17">
         <v>40.333333333333336</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B17">
+      <c r="C18">
         <v>37.663617886178862</v>
       </c>
     </row>
@@ -65817,14 +65815,14 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="23"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
@@ -65839,19 +65837,19 @@
       <c r="D4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>56</v>
+      <c r="E4" s="18" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="2">
         <v>66</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
         <v>66</v>
       </c>
       <c r="E5" s="14">
@@ -65863,13 +65861,13 @@
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="2">
         <v>33</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="2">
         <v>33</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="2">
         <v>66</v>
       </c>
       <c r="E6" s="14">
@@ -65881,13 +65879,13 @@
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="2">
         <v>33</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="2">
         <v>33</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="2">
         <v>66</v>
       </c>
       <c r="E7" s="14">
@@ -65899,11 +65897,11 @@
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="2">
         <v>65</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
         <v>65</v>
       </c>
       <c r="E8" s="14">
@@ -65915,13 +65913,13 @@
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="2">
         <v>64</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="2">
         <v>65</v>
       </c>
       <c r="E9" s="14">
@@ -65933,13 +65931,13 @@
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="2">
         <v>33</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="2">
         <v>33</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="2">
         <v>66</v>
       </c>
       <c r="E10" s="14">
@@ -65951,11 +65949,11 @@
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="2">
         <v>67</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
         <v>67</v>
       </c>
       <c r="E11" s="14">
@@ -65967,11 +65965,11 @@
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2">
         <v>67</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="2">
         <v>67</v>
       </c>
       <c r="E12" s="14">
@@ -65983,13 +65981,13 @@
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="2">
         <v>1</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="2">
         <v>64</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="2">
         <v>65</v>
       </c>
       <c r="E13" s="14">
@@ -66001,11 +65999,11 @@
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="2">
         <v>66</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
         <v>66</v>
       </c>
       <c r="E14" s="14">
@@ -66017,11 +66015,11 @@
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="2">
         <v>65</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2">
         <v>65</v>
       </c>
       <c r="E15" s="14">
@@ -66033,11 +66031,11 @@
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="2">
         <v>64</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
         <v>64</v>
       </c>
       <c r="E16" s="14">
@@ -66049,11 +66047,11 @@
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="2">
         <v>65</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
         <v>65</v>
       </c>
       <c r="E17" s="14">
@@ -66065,11 +66063,11 @@
       <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="2">
         <v>65</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2">
         <v>65</v>
       </c>
       <c r="E18" s="14">
@@ -66081,13 +66079,13 @@
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="2">
         <v>33</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="2">
         <v>33</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="2">
         <v>66</v>
       </c>
       <c r="E19" s="14">
@@ -66099,16 +66097,16 @@
       <c r="A20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="2">
         <v>720</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="2">
         <v>264</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="2">
         <v>984</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="17">
         <f t="shared" si="0"/>
         <v>0.26829268292682928</v>
       </c>
@@ -66139,1282 +66137,1282 @@
   </cols>
   <sheetData>
     <row r="6" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="24"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
     </row>
     <row r="7" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="24"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="19"/>
     </row>
     <row r="8" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="24"/>
-      <c r="AH8" s="24"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="19"/>
+      <c r="AG8" s="19"/>
+      <c r="AH8" s="19"/>
     </row>
     <row r="9" spans="8:34" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="24"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="24"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="19"/>
+      <c r="AG9" s="19"/>
+      <c r="AH9" s="19"/>
     </row>
     <row r="10" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="24"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+      <c r="AD10" s="19"/>
+      <c r="AE10" s="19"/>
+      <c r="AF10" s="19"/>
+      <c r="AG10" s="19"/>
+      <c r="AH10" s="19"/>
     </row>
     <row r="11" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="24"/>
-      <c r="AH11" s="24"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+      <c r="AH11" s="19"/>
     </row>
     <row r="12" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="24"/>
-      <c r="AH12" s="24"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="19"/>
+      <c r="AG12" s="19"/>
+      <c r="AH12" s="19"/>
     </row>
     <row r="13" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="24"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="19"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="19"/>
     </row>
     <row r="14" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="24"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="19"/>
+      <c r="AC14" s="19"/>
+      <c r="AD14" s="19"/>
+      <c r="AE14" s="19"/>
+      <c r="AF14" s="19"/>
+      <c r="AG14" s="19"/>
+      <c r="AH14" s="19"/>
     </row>
     <row r="15" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
-      <c r="AH15" s="24"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+      <c r="AD15" s="19"/>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="19"/>
+      <c r="AG15" s="19"/>
+      <c r="AH15" s="19"/>
     </row>
     <row r="16" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
-      <c r="AH16" s="24"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
+      <c r="AC16" s="19"/>
+      <c r="AD16" s="19"/>
+      <c r="AE16" s="19"/>
+      <c r="AF16" s="19"/>
+      <c r="AG16" s="19"/>
+      <c r="AH16" s="19"/>
     </row>
     <row r="17" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
-      <c r="AH17" s="24"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="19"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="19"/>
+      <c r="AC17" s="19"/>
+      <c r="AD17" s="19"/>
+      <c r="AE17" s="19"/>
+      <c r="AF17" s="19"/>
+      <c r="AG17" s="19"/>
+      <c r="AH17" s="19"/>
     </row>
     <row r="18" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="24"/>
-      <c r="AH18" s="24"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
+      <c r="AA18" s="19"/>
+      <c r="AB18" s="19"/>
+      <c r="AC18" s="19"/>
+      <c r="AD18" s="19"/>
+      <c r="AE18" s="19"/>
+      <c r="AF18" s="19"/>
+      <c r="AG18" s="19"/>
+      <c r="AH18" s="19"/>
     </row>
     <row r="19" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="24"/>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="24"/>
-      <c r="AH19" s="24"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="19"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="19"/>
+      <c r="AE19" s="19"/>
+      <c r="AF19" s="19"/>
+      <c r="AG19" s="19"/>
+      <c r="AH19" s="19"/>
     </row>
     <row r="20" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
+      <c r="AA20" s="19"/>
+      <c r="AB20" s="19"/>
+      <c r="AC20" s="19"/>
+      <c r="AD20" s="19"/>
+      <c r="AE20" s="19"/>
+      <c r="AF20" s="19"/>
+      <c r="AG20" s="19"/>
+      <c r="AH20" s="19"/>
     </row>
     <row r="21" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="19"/>
+      <c r="Z21" s="19"/>
+      <c r="AA21" s="19"/>
+      <c r="AB21" s="19"/>
+      <c r="AC21" s="19"/>
+      <c r="AD21" s="19"/>
+      <c r="AE21" s="19"/>
+      <c r="AF21" s="19"/>
+      <c r="AG21" s="19"/>
+      <c r="AH21" s="19"/>
     </row>
     <row r="22" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="24"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="24"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="24"/>
-      <c r="AH22" s="24"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="19"/>
+      <c r="AA22" s="19"/>
+      <c r="AB22" s="19"/>
+      <c r="AC22" s="19"/>
+      <c r="AD22" s="19"/>
+      <c r="AE22" s="19"/>
+      <c r="AF22" s="19"/>
+      <c r="AG22" s="19"/>
+      <c r="AH22" s="19"/>
     </row>
     <row r="23" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="24"/>
-      <c r="AA23" s="24"/>
-      <c r="AB23" s="24"/>
-      <c r="AC23" s="24"/>
-      <c r="AD23" s="24"/>
-      <c r="AE23" s="24"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="24"/>
-      <c r="AH23" s="24"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="19"/>
+      <c r="AA23" s="19"/>
+      <c r="AB23" s="19"/>
+      <c r="AC23" s="19"/>
+      <c r="AD23" s="19"/>
+      <c r="AE23" s="19"/>
+      <c r="AF23" s="19"/>
+      <c r="AG23" s="19"/>
+      <c r="AH23" s="19"/>
     </row>
     <row r="24" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="24"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="24"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="24"/>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="24"/>
-      <c r="AH24" s="24"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="19"/>
+      <c r="AB24" s="19"/>
+      <c r="AC24" s="19"/>
+      <c r="AD24" s="19"/>
+      <c r="AE24" s="19"/>
+      <c r="AF24" s="19"/>
+      <c r="AG24" s="19"/>
+      <c r="AH24" s="19"/>
     </row>
     <row r="25" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="24"/>
-      <c r="AD25" s="24"/>
-      <c r="AE25" s="24"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="24"/>
-      <c r="AH25" s="24"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="19"/>
+      <c r="AB25" s="19"/>
+      <c r="AC25" s="19"/>
+      <c r="AD25" s="19"/>
+      <c r="AE25" s="19"/>
+      <c r="AF25" s="19"/>
+      <c r="AG25" s="19"/>
+      <c r="AH25" s="19"/>
     </row>
     <row r="26" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
-      <c r="U26" s="24"/>
-      <c r="V26" s="24"/>
-      <c r="W26" s="24"/>
-      <c r="X26" s="24"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="24"/>
-      <c r="AA26" s="24"/>
-      <c r="AB26" s="24"/>
-      <c r="AC26" s="24"/>
-      <c r="AD26" s="24"/>
-      <c r="AE26" s="24"/>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="24"/>
-      <c r="AH26" s="24"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="19"/>
+      <c r="AA26" s="19"/>
+      <c r="AB26" s="19"/>
+      <c r="AC26" s="19"/>
+      <c r="AD26" s="19"/>
+      <c r="AE26" s="19"/>
+      <c r="AF26" s="19"/>
+      <c r="AG26" s="19"/>
+      <c r="AH26" s="19"/>
     </row>
     <row r="27" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="24"/>
-      <c r="T27" s="24"/>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="24"/>
-      <c r="AC27" s="24"/>
-      <c r="AD27" s="24"/>
-      <c r="AE27" s="24"/>
-      <c r="AF27" s="24"/>
-      <c r="AG27" s="24"/>
-      <c r="AH27" s="24"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="19"/>
+      <c r="Z27" s="19"/>
+      <c r="AA27" s="19"/>
+      <c r="AB27" s="19"/>
+      <c r="AC27" s="19"/>
+      <c r="AD27" s="19"/>
+      <c r="AE27" s="19"/>
+      <c r="AF27" s="19"/>
+      <c r="AG27" s="19"/>
+      <c r="AH27" s="19"/>
     </row>
     <row r="28" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="24"/>
-      <c r="AC28" s="24"/>
-      <c r="AD28" s="24"/>
-      <c r="AE28" s="24"/>
-      <c r="AF28" s="24"/>
-      <c r="AG28" s="24"/>
-      <c r="AH28" s="24"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="19"/>
+      <c r="AA28" s="19"/>
+      <c r="AB28" s="19"/>
+      <c r="AC28" s="19"/>
+      <c r="AD28" s="19"/>
+      <c r="AE28" s="19"/>
+      <c r="AF28" s="19"/>
+      <c r="AG28" s="19"/>
+      <c r="AH28" s="19"/>
     </row>
     <row r="29" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
-      <c r="V29" s="24"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="24"/>
-      <c r="AB29" s="24"/>
-      <c r="AC29" s="24"/>
-      <c r="AD29" s="24"/>
-      <c r="AE29" s="24"/>
-      <c r="AF29" s="24"/>
-      <c r="AG29" s="24"/>
-      <c r="AH29" s="24"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="19"/>
+      <c r="AA29" s="19"/>
+      <c r="AB29" s="19"/>
+      <c r="AC29" s="19"/>
+      <c r="AD29" s="19"/>
+      <c r="AE29" s="19"/>
+      <c r="AF29" s="19"/>
+      <c r="AG29" s="19"/>
+      <c r="AH29" s="19"/>
     </row>
     <row r="30" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
-      <c r="R30" s="24"/>
-      <c r="S30" s="24"/>
-      <c r="T30" s="24"/>
-      <c r="U30" s="24"/>
-      <c r="V30" s="24"/>
-      <c r="W30" s="24"/>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="24"/>
-      <c r="AA30" s="24"/>
-      <c r="AB30" s="24"/>
-      <c r="AC30" s="24"/>
-      <c r="AD30" s="24"/>
-      <c r="AE30" s="24"/>
-      <c r="AF30" s="24"/>
-      <c r="AG30" s="24"/>
-      <c r="AH30" s="24"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="19"/>
+      <c r="Z30" s="19"/>
+      <c r="AA30" s="19"/>
+      <c r="AB30" s="19"/>
+      <c r="AC30" s="19"/>
+      <c r="AD30" s="19"/>
+      <c r="AE30" s="19"/>
+      <c r="AF30" s="19"/>
+      <c r="AG30" s="19"/>
+      <c r="AH30" s="19"/>
     </row>
     <row r="31" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
-      <c r="R31" s="24"/>
-      <c r="S31" s="24"/>
-      <c r="T31" s="24"/>
-      <c r="U31" s="24"/>
-      <c r="V31" s="24"/>
-      <c r="W31" s="24"/>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="24"/>
-      <c r="AA31" s="24"/>
-      <c r="AB31" s="24"/>
-      <c r="AC31" s="24"/>
-      <c r="AD31" s="24"/>
-      <c r="AE31" s="24"/>
-      <c r="AF31" s="24"/>
-      <c r="AG31" s="24"/>
-      <c r="AH31" s="24"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="19"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="19"/>
+      <c r="Y31" s="19"/>
+      <c r="Z31" s="19"/>
+      <c r="AA31" s="19"/>
+      <c r="AB31" s="19"/>
+      <c r="AC31" s="19"/>
+      <c r="AD31" s="19"/>
+      <c r="AE31" s="19"/>
+      <c r="AF31" s="19"/>
+      <c r="AG31" s="19"/>
+      <c r="AH31" s="19"/>
     </row>
     <row r="32" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="24"/>
-      <c r="R32" s="24"/>
-      <c r="S32" s="24"/>
-      <c r="T32" s="24"/>
-      <c r="U32" s="24"/>
-      <c r="V32" s="24"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="24"/>
-      <c r="AA32" s="24"/>
-      <c r="AB32" s="24"/>
-      <c r="AC32" s="24"/>
-      <c r="AD32" s="24"/>
-      <c r="AE32" s="24"/>
-      <c r="AF32" s="24"/>
-      <c r="AG32" s="24"/>
-      <c r="AH32" s="24"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="19"/>
+      <c r="Z32" s="19"/>
+      <c r="AA32" s="19"/>
+      <c r="AB32" s="19"/>
+      <c r="AC32" s="19"/>
+      <c r="AD32" s="19"/>
+      <c r="AE32" s="19"/>
+      <c r="AF32" s="19"/>
+      <c r="AG32" s="19"/>
+      <c r="AH32" s="19"/>
     </row>
     <row r="33" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="24"/>
-      <c r="R33" s="24"/>
-      <c r="S33" s="24"/>
-      <c r="T33" s="24"/>
-      <c r="U33" s="24"/>
-      <c r="V33" s="24"/>
-      <c r="W33" s="24"/>
-      <c r="X33" s="24"/>
-      <c r="Y33" s="24"/>
-      <c r="Z33" s="24"/>
-      <c r="AA33" s="24"/>
-      <c r="AB33" s="24"/>
-      <c r="AC33" s="24"/>
-      <c r="AD33" s="24"/>
-      <c r="AE33" s="24"/>
-      <c r="AF33" s="24"/>
-      <c r="AG33" s="24"/>
-      <c r="AH33" s="24"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="19"/>
+      <c r="Y33" s="19"/>
+      <c r="Z33" s="19"/>
+      <c r="AA33" s="19"/>
+      <c r="AB33" s="19"/>
+      <c r="AC33" s="19"/>
+      <c r="AD33" s="19"/>
+      <c r="AE33" s="19"/>
+      <c r="AF33" s="19"/>
+      <c r="AG33" s="19"/>
+      <c r="AH33" s="19"/>
     </row>
     <row r="34" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="24"/>
-      <c r="R34" s="24"/>
-      <c r="S34" s="24"/>
-      <c r="T34" s="24"/>
-      <c r="U34" s="24"/>
-      <c r="V34" s="24"/>
-      <c r="W34" s="24"/>
-      <c r="X34" s="24"/>
-      <c r="Y34" s="24"/>
-      <c r="Z34" s="24"/>
-      <c r="AA34" s="24"/>
-      <c r="AB34" s="24"/>
-      <c r="AC34" s="24"/>
-      <c r="AD34" s="24"/>
-      <c r="AE34" s="24"/>
-      <c r="AF34" s="24"/>
-      <c r="AG34" s="24"/>
-      <c r="AH34" s="24"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="19"/>
+      <c r="X34" s="19"/>
+      <c r="Y34" s="19"/>
+      <c r="Z34" s="19"/>
+      <c r="AA34" s="19"/>
+      <c r="AB34" s="19"/>
+      <c r="AC34" s="19"/>
+      <c r="AD34" s="19"/>
+      <c r="AE34" s="19"/>
+      <c r="AF34" s="19"/>
+      <c r="AG34" s="19"/>
+      <c r="AH34" s="19"/>
     </row>
     <row r="35" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="24"/>
-      <c r="U35" s="24"/>
-      <c r="V35" s="24"/>
-      <c r="W35" s="24"/>
-      <c r="X35" s="24"/>
-      <c r="Y35" s="24"/>
-      <c r="Z35" s="24"/>
-      <c r="AA35" s="24"/>
-      <c r="AB35" s="24"/>
-      <c r="AC35" s="24"/>
-      <c r="AD35" s="24"/>
-      <c r="AE35" s="24"/>
-      <c r="AF35" s="24"/>
-      <c r="AG35" s="24"/>
-      <c r="AH35" s="24"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="19"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="19"/>
+      <c r="X35" s="19"/>
+      <c r="Y35" s="19"/>
+      <c r="Z35" s="19"/>
+      <c r="AA35" s="19"/>
+      <c r="AB35" s="19"/>
+      <c r="AC35" s="19"/>
+      <c r="AD35" s="19"/>
+      <c r="AE35" s="19"/>
+      <c r="AF35" s="19"/>
+      <c r="AG35" s="19"/>
+      <c r="AH35" s="19"/>
     </row>
     <row r="36" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="24"/>
-      <c r="AB36" s="24"/>
-      <c r="AC36" s="24"/>
-      <c r="AD36" s="24"/>
-      <c r="AE36" s="24"/>
-      <c r="AF36" s="24"/>
-      <c r="AG36" s="24"/>
-      <c r="AH36" s="24"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="19"/>
+      <c r="U36" s="19"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="19"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="19"/>
+      <c r="Z36" s="19"/>
+      <c r="AA36" s="19"/>
+      <c r="AB36" s="19"/>
+      <c r="AC36" s="19"/>
+      <c r="AD36" s="19"/>
+      <c r="AE36" s="19"/>
+      <c r="AF36" s="19"/>
+      <c r="AG36" s="19"/>
+      <c r="AH36" s="19"/>
     </row>
     <row r="37" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="24"/>
-      <c r="U37" s="24"/>
-      <c r="V37" s="24"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
-      <c r="Z37" s="24"/>
-      <c r="AA37" s="24"/>
-      <c r="AB37" s="24"/>
-      <c r="AC37" s="24"/>
-      <c r="AD37" s="24"/>
-      <c r="AE37" s="24"/>
-      <c r="AF37" s="24"/>
-      <c r="AG37" s="24"/>
-      <c r="AH37" s="24"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="19"/>
+      <c r="U37" s="19"/>
+      <c r="V37" s="19"/>
+      <c r="W37" s="19"/>
+      <c r="X37" s="19"/>
+      <c r="Y37" s="19"/>
+      <c r="Z37" s="19"/>
+      <c r="AA37" s="19"/>
+      <c r="AB37" s="19"/>
+      <c r="AC37" s="19"/>
+      <c r="AD37" s="19"/>
+      <c r="AE37" s="19"/>
+      <c r="AF37" s="19"/>
+      <c r="AG37" s="19"/>
+      <c r="AH37" s="19"/>
     </row>
     <row r="38" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="24"/>
-      <c r="U38" s="24"/>
-      <c r="V38" s="24"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="24"/>
-      <c r="Y38" s="24"/>
-      <c r="Z38" s="24"/>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="24"/>
-      <c r="AC38" s="24"/>
-      <c r="AD38" s="24"/>
-      <c r="AE38" s="24"/>
-      <c r="AF38" s="24"/>
-      <c r="AG38" s="24"/>
-      <c r="AH38" s="24"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="19"/>
+      <c r="U38" s="19"/>
+      <c r="V38" s="19"/>
+      <c r="W38" s="19"/>
+      <c r="X38" s="19"/>
+      <c r="Y38" s="19"/>
+      <c r="Z38" s="19"/>
+      <c r="AA38" s="19"/>
+      <c r="AB38" s="19"/>
+      <c r="AC38" s="19"/>
+      <c r="AD38" s="19"/>
+      <c r="AE38" s="19"/>
+      <c r="AF38" s="19"/>
+      <c r="AG38" s="19"/>
+      <c r="AH38" s="19"/>
     </row>
     <row r="39" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="24"/>
-      <c r="R39" s="24"/>
-      <c r="S39" s="24"/>
-      <c r="T39" s="24"/>
-      <c r="U39" s="24"/>
-      <c r="V39" s="24"/>
-      <c r="W39" s="24"/>
-      <c r="X39" s="24"/>
-      <c r="Y39" s="24"/>
-      <c r="Z39" s="24"/>
-      <c r="AA39" s="24"/>
-      <c r="AB39" s="24"/>
-      <c r="AC39" s="24"/>
-      <c r="AD39" s="24"/>
-      <c r="AE39" s="24"/>
-      <c r="AF39" s="24"/>
-      <c r="AG39" s="24"/>
-      <c r="AH39" s="24"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="19"/>
+      <c r="U39" s="19"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19"/>
+      <c r="Z39" s="19"/>
+      <c r="AA39" s="19"/>
+      <c r="AB39" s="19"/>
+      <c r="AC39" s="19"/>
+      <c r="AD39" s="19"/>
+      <c r="AE39" s="19"/>
+      <c r="AF39" s="19"/>
+      <c r="AG39" s="19"/>
+      <c r="AH39" s="19"/>
     </row>
     <row r="40" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
-      <c r="W40" s="24"/>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="24"/>
-      <c r="Z40" s="24"/>
-      <c r="AA40" s="24"/>
-      <c r="AB40" s="24"/>
-      <c r="AC40" s="24"/>
-      <c r="AD40" s="24"/>
-      <c r="AE40" s="24"/>
-      <c r="AF40" s="24"/>
-      <c r="AG40" s="24"/>
-      <c r="AH40" s="24"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="19"/>
+      <c r="AA40" s="19"/>
+      <c r="AB40" s="19"/>
+      <c r="AC40" s="19"/>
+      <c r="AD40" s="19"/>
+      <c r="AE40" s="19"/>
+      <c r="AF40" s="19"/>
+      <c r="AG40" s="19"/>
+      <c r="AH40" s="19"/>
     </row>
     <row r="41" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="24"/>
-      <c r="R41" s="24"/>
-      <c r="S41" s="24"/>
-      <c r="T41" s="24"/>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
-      <c r="W41" s="24"/>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="24"/>
-      <c r="Z41" s="24"/>
-      <c r="AA41" s="24"/>
-      <c r="AB41" s="24"/>
-      <c r="AC41" s="24"/>
-      <c r="AD41" s="24"/>
-      <c r="AE41" s="24"/>
-      <c r="AF41" s="24"/>
-      <c r="AG41" s="24"/>
-      <c r="AH41" s="24"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="19"/>
+      <c r="AA41" s="19"/>
+      <c r="AB41" s="19"/>
+      <c r="AC41" s="19"/>
+      <c r="AD41" s="19"/>
+      <c r="AE41" s="19"/>
+      <c r="AF41" s="19"/>
+      <c r="AG41" s="19"/>
+      <c r="AH41" s="19"/>
     </row>
     <row r="42" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
-      <c r="R42" s="24"/>
-      <c r="S42" s="24"/>
-      <c r="T42" s="24"/>
-      <c r="U42" s="24"/>
-      <c r="V42" s="24"/>
-      <c r="W42" s="24"/>
-      <c r="X42" s="24"/>
-      <c r="Y42" s="24"/>
-      <c r="Z42" s="24"/>
-      <c r="AA42" s="24"/>
-      <c r="AB42" s="24"/>
-      <c r="AC42" s="24"/>
-      <c r="AD42" s="24"/>
-      <c r="AE42" s="24"/>
-      <c r="AF42" s="24"/>
-      <c r="AG42" s="24"/>
-      <c r="AH42" s="24"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="19"/>
+      <c r="U42" s="19"/>
+      <c r="V42" s="19"/>
+      <c r="W42" s="19"/>
+      <c r="X42" s="19"/>
+      <c r="Y42" s="19"/>
+      <c r="Z42" s="19"/>
+      <c r="AA42" s="19"/>
+      <c r="AB42" s="19"/>
+      <c r="AC42" s="19"/>
+      <c r="AD42" s="19"/>
+      <c r="AE42" s="19"/>
+      <c r="AF42" s="19"/>
+      <c r="AG42" s="19"/>
+      <c r="AH42" s="19"/>
     </row>
     <row r="43" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="24"/>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="24"/>
-      <c r="R43" s="24"/>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="24"/>
-      <c r="AA43" s="24"/>
-      <c r="AB43" s="24"/>
-      <c r="AC43" s="24"/>
-      <c r="AD43" s="24"/>
-      <c r="AE43" s="24"/>
-      <c r="AF43" s="24"/>
-      <c r="AG43" s="24"/>
-      <c r="AH43" s="24"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="19"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="19"/>
+      <c r="U43" s="19"/>
+      <c r="V43" s="19"/>
+      <c r="W43" s="19"/>
+      <c r="X43" s="19"/>
+      <c r="Y43" s="19"/>
+      <c r="Z43" s="19"/>
+      <c r="AA43" s="19"/>
+      <c r="AB43" s="19"/>
+      <c r="AC43" s="19"/>
+      <c r="AD43" s="19"/>
+      <c r="AE43" s="19"/>
+      <c r="AF43" s="19"/>
+      <c r="AG43" s="19"/>
+      <c r="AH43" s="19"/>
     </row>
     <row r="44" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="24"/>
-      <c r="N44" s="24"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="24"/>
-      <c r="Q44" s="24"/>
-      <c r="R44" s="24"/>
-      <c r="S44" s="24"/>
-      <c r="T44" s="24"/>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="24"/>
-      <c r="X44" s="24"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="24"/>
-      <c r="AC44" s="24"/>
-      <c r="AD44" s="24"/>
-      <c r="AE44" s="24"/>
-      <c r="AF44" s="24"/>
-      <c r="AG44" s="24"/>
-      <c r="AH44" s="24"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="19"/>
+      <c r="T44" s="19"/>
+      <c r="U44" s="19"/>
+      <c r="V44" s="19"/>
+      <c r="W44" s="19"/>
+      <c r="X44" s="19"/>
+      <c r="Y44" s="19"/>
+      <c r="Z44" s="19"/>
+      <c r="AA44" s="19"/>
+      <c r="AB44" s="19"/>
+      <c r="AC44" s="19"/>
+      <c r="AD44" s="19"/>
+      <c r="AE44" s="19"/>
+      <c r="AF44" s="19"/>
+      <c r="AG44" s="19"/>
+      <c r="AH44" s="19"/>
     </row>
     <row r="45" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H45" s="24"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="24"/>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="24"/>
-      <c r="N45" s="24"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="24"/>
-      <c r="Q45" s="24"/>
-      <c r="R45" s="24"/>
-      <c r="S45" s="24"/>
-      <c r="T45" s="24"/>
-      <c r="U45" s="24"/>
-      <c r="V45" s="24"/>
-      <c r="W45" s="24"/>
-      <c r="X45" s="24"/>
-      <c r="Y45" s="24"/>
-      <c r="Z45" s="24"/>
-      <c r="AA45" s="24"/>
-      <c r="AB45" s="24"/>
-      <c r="AC45" s="24"/>
-      <c r="AD45" s="24"/>
-      <c r="AE45" s="24"/>
-      <c r="AF45" s="24"/>
-      <c r="AG45" s="24"/>
-      <c r="AH45" s="24"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="19"/>
+      <c r="U45" s="19"/>
+      <c r="V45" s="19"/>
+      <c r="W45" s="19"/>
+      <c r="X45" s="19"/>
+      <c r="Y45" s="19"/>
+      <c r="Z45" s="19"/>
+      <c r="AA45" s="19"/>
+      <c r="AB45" s="19"/>
+      <c r="AC45" s="19"/>
+      <c r="AD45" s="19"/>
+      <c r="AE45" s="19"/>
+      <c r="AF45" s="19"/>
+      <c r="AG45" s="19"/>
+      <c r="AH45" s="19"/>
     </row>
     <row r="46" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="24"/>
-      <c r="N46" s="24"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="24"/>
-      <c r="Q46" s="24"/>
-      <c r="R46" s="24"/>
-      <c r="S46" s="24"/>
-      <c r="T46" s="24"/>
-      <c r="U46" s="24"/>
-      <c r="V46" s="24"/>
-      <c r="W46" s="24"/>
-      <c r="X46" s="24"/>
-      <c r="Y46" s="24"/>
-      <c r="Z46" s="24"/>
-      <c r="AA46" s="24"/>
-      <c r="AB46" s="24"/>
-      <c r="AC46" s="24"/>
-      <c r="AD46" s="24"/>
-      <c r="AE46" s="24"/>
-      <c r="AF46" s="24"/>
-      <c r="AG46" s="24"/>
-      <c r="AH46" s="24"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="19"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="19"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="19"/>
+      <c r="U46" s="19"/>
+      <c r="V46" s="19"/>
+      <c r="W46" s="19"/>
+      <c r="X46" s="19"/>
+      <c r="Y46" s="19"/>
+      <c r="Z46" s="19"/>
+      <c r="AA46" s="19"/>
+      <c r="AB46" s="19"/>
+      <c r="AC46" s="19"/>
+      <c r="AD46" s="19"/>
+      <c r="AE46" s="19"/>
+      <c r="AF46" s="19"/>
+      <c r="AG46" s="19"/>
+      <c r="AH46" s="19"/>
     </row>
     <row r="47" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="24"/>
-      <c r="N47" s="24"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="24"/>
-      <c r="Q47" s="24"/>
-      <c r="R47" s="24"/>
-      <c r="S47" s="24"/>
-      <c r="T47" s="24"/>
-      <c r="U47" s="24"/>
-      <c r="V47" s="24"/>
-      <c r="W47" s="24"/>
-      <c r="X47" s="24"/>
-      <c r="Y47" s="24"/>
-      <c r="Z47" s="24"/>
-      <c r="AA47" s="24"/>
-      <c r="AB47" s="24"/>
-      <c r="AC47" s="24"/>
-      <c r="AD47" s="24"/>
-      <c r="AE47" s="24"/>
-      <c r="AF47" s="24"/>
-      <c r="AG47" s="24"/>
-      <c r="AH47" s="24"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="19"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="19"/>
+      <c r="R47" s="19"/>
+      <c r="S47" s="19"/>
+      <c r="T47" s="19"/>
+      <c r="U47" s="19"/>
+      <c r="V47" s="19"/>
+      <c r="W47" s="19"/>
+      <c r="X47" s="19"/>
+      <c r="Y47" s="19"/>
+      <c r="Z47" s="19"/>
+      <c r="AA47" s="19"/>
+      <c r="AB47" s="19"/>
+      <c r="AC47" s="19"/>
+      <c r="AD47" s="19"/>
+      <c r="AE47" s="19"/>
+      <c r="AF47" s="19"/>
+      <c r="AG47" s="19"/>
+      <c r="AH47" s="19"/>
     </row>
     <row r="48" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="24"/>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="24"/>
-      <c r="R48" s="24"/>
-      <c r="S48" s="24"/>
-      <c r="T48" s="24"/>
-      <c r="U48" s="24"/>
-      <c r="V48" s="24"/>
-      <c r="W48" s="24"/>
-      <c r="X48" s="24"/>
-      <c r="Y48" s="24"/>
-      <c r="Z48" s="24"/>
-      <c r="AA48" s="24"/>
-      <c r="AB48" s="24"/>
-      <c r="AC48" s="24"/>
-      <c r="AD48" s="24"/>
-      <c r="AE48" s="24"/>
-      <c r="AF48" s="24"/>
-      <c r="AG48" s="24"/>
-      <c r="AH48" s="24"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
+      <c r="O48" s="19"/>
+      <c r="P48" s="19"/>
+      <c r="Q48" s="19"/>
+      <c r="R48" s="19"/>
+      <c r="S48" s="19"/>
+      <c r="T48" s="19"/>
+      <c r="U48" s="19"/>
+      <c r="V48" s="19"/>
+      <c r="W48" s="19"/>
+      <c r="X48" s="19"/>
+      <c r="Y48" s="19"/>
+      <c r="Z48" s="19"/>
+      <c r="AA48" s="19"/>
+      <c r="AB48" s="19"/>
+      <c r="AC48" s="19"/>
+      <c r="AD48" s="19"/>
+      <c r="AE48" s="19"/>
+      <c r="AF48" s="19"/>
+      <c r="AG48" s="19"/>
+      <c r="AH48" s="19"/>
     </row>
     <row r="49" spans="8:34" x14ac:dyDescent="0.3">
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="24"/>
-      <c r="N49" s="24"/>
-      <c r="O49" s="24"/>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="24"/>
-      <c r="R49" s="24"/>
-      <c r="S49" s="24"/>
-      <c r="T49" s="24"/>
-      <c r="U49" s="24"/>
-      <c r="V49" s="24"/>
-      <c r="W49" s="24"/>
-      <c r="X49" s="24"/>
-      <c r="Y49" s="24"/>
-      <c r="Z49" s="24"/>
-      <c r="AA49" s="24"/>
-      <c r="AB49" s="24"/>
-      <c r="AC49" s="24"/>
-      <c r="AD49" s="24"/>
-      <c r="AE49" s="24"/>
-      <c r="AF49" s="24"/>
-      <c r="AG49" s="24"/>
-      <c r="AH49" s="24"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="19"/>
+      <c r="S49" s="19"/>
+      <c r="T49" s="19"/>
+      <c r="U49" s="19"/>
+      <c r="V49" s="19"/>
+      <c r="W49" s="19"/>
+      <c r="X49" s="19"/>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="19"/>
+      <c r="AA49" s="19"/>
+      <c r="AB49" s="19"/>
+      <c r="AC49" s="19"/>
+      <c r="AD49" s="19"/>
+      <c r="AE49" s="19"/>
+      <c r="AF49" s="19"/>
+      <c r="AG49" s="19"/>
+      <c r="AH49" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
